--- a/docs/usuarios.xlsx
+++ b/docs/usuarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d9cd9fa3079768ea/Desktop/CONFIRMACION PREVIA/backend/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{31CC0195-0B93-4CB5-BEFE-5079A7CDEDB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{31CC0195-0B93-4CB5-BEFE-5079A7CDEDB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EFAECDE-22CC-4D43-AA92-761A249C8283}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E85F2AEF-B07F-4CC1-86F8-9892FA91C6C6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="23">
   <si>
     <t>USERNAME</t>
   </si>
@@ -36,22 +36,64 @@
     <t>ROL</t>
   </si>
   <si>
-    <t>sebas</t>
-  </si>
-  <si>
-    <t>xd</t>
-  </si>
-  <si>
     <t>admin</t>
   </si>
   <si>
-    <t>jose</t>
-  </si>
-  <si>
-    <t>amd</t>
-  </si>
-  <si>
     <t>user</t>
+  </si>
+  <si>
+    <t>Ajila Guaman Alison Pamela</t>
+  </si>
+  <si>
+    <t>Ayala Echeverría Pablo Fernando</t>
+  </si>
+  <si>
+    <t>Centeno Andrade Neider Joel</t>
+  </si>
+  <si>
+    <t>Cervantes Paredes Mariuxy Alexandra</t>
+  </si>
+  <si>
+    <t>Cordova Jaramillo Maria Beatriz</t>
+  </si>
+  <si>
+    <t>Esquivel Miño Johanna Elizabeth</t>
+  </si>
+  <si>
+    <t>Gallegos Torres Ana Maria</t>
+  </si>
+  <si>
+    <t>Jacome Flores Michelle Isabel</t>
+  </si>
+  <si>
+    <t>Lopez Molina Alejandra Cristina</t>
+  </si>
+  <si>
+    <t>Najera Suarez Diana Karina</t>
+  </si>
+  <si>
+    <t>Paillacho Gusque Daniela Estefania</t>
+  </si>
+  <si>
+    <t>Ponce Calucho Clara Janeth</t>
+  </si>
+  <si>
+    <t>Sanchez Paztrana Rosa Estefania</t>
+  </si>
+  <si>
+    <t>Sanchez Tutillo Paola Alexandra</t>
+  </si>
+  <si>
+    <t>Toaza Benitez Jeanneth Cristina</t>
+  </si>
+  <si>
+    <t>Zambrano Farias Lisbeth Carolina</t>
+  </si>
+  <si>
+    <t>Guachichulca Ponce Alan Joel</t>
+  </si>
+  <si>
+    <t>José Elizalde</t>
   </si>
 </sst>
 </file>
@@ -403,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06BEE497-F520-4DE3-B9B2-36EAB11B4C8E}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -419,24 +461,200 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>1726437468</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3">
+        <v>1716450653</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B4">
+        <v>1752397891</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1723536031</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>1721382024</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>1721811840</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>1712014396</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
+        <v>1727016642</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
+        <v>1719874438</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11">
+        <v>1205646977</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <v>1750854877</v>
+      </c>
+      <c r="C12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13">
+        <v>1719082222</v>
+      </c>
+      <c r="C13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14">
+        <v>1724783376</v>
+      </c>
+      <c r="C14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15">
+        <v>1715607808</v>
+      </c>
+      <c r="C15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16">
+        <v>1718528837</v>
+      </c>
+      <c r="C16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17">
+        <v>1755075510</v>
+      </c>
+      <c r="C17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18">
+        <v>1755637079</v>
+      </c>
+      <c r="C18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19">
+        <v>1718773664</v>
+      </c>
+      <c r="C19" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docs/usuarios.xlsx
+++ b/docs/usuarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d9cd9fa3079768ea/Desktop/CONFIRMACION PREVIA/backend/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="8_{31CC0195-0B93-4CB5-BEFE-5079A7CDEDB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EFAECDE-22CC-4D43-AA92-761A249C8283}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{31CC0195-0B93-4CB5-BEFE-5079A7CDEDB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8515AD33-5255-42D6-A3CC-C21E837855AA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E85F2AEF-B07F-4CC1-86F8-9892FA91C6C6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="22">
   <si>
     <t>USERNAME</t>
   </si>
@@ -91,9 +91,6 @@
   </si>
   <si>
     <t>Guachichulca Ponce Alan Joel</t>
-  </si>
-  <si>
-    <t>José Elizalde</t>
   </si>
 </sst>
 </file>
@@ -445,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06BEE497-F520-4DE3-B9B2-36EAB11B4C8E}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -646,17 +643,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19">
-        <v>1718773664</v>
-      </c>
-      <c r="C19" t="s">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/usuarios.xlsx
+++ b/docs/usuarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d9cd9fa3079768ea/Desktop/CONFIRMACION PREVIA/backend/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{31CC0195-0B93-4CB5-BEFE-5079A7CDEDB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8515AD33-5255-42D6-A3CC-C21E837855AA}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{31CC0195-0B93-4CB5-BEFE-5079A7CDEDB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38458DC1-405A-4FD3-8CB8-3810D2290BB5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E85F2AEF-B07F-4CC1-86F8-9892FA91C6C6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="23">
   <si>
     <t>USERNAME</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Guachichulca Ponce Alan Joel</t>
+  </si>
+  <si>
+    <t>Pazmiño Cruz Sebastián Andrés</t>
   </si>
 </sst>
 </file>
@@ -442,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06BEE497-F520-4DE3-B9B2-36EAB11B4C8E}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -643,6 +646,17 @@
         <v>4</v>
       </c>
     </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19">
+        <v>1723594907</v>
+      </c>
+      <c r="C19" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
